--- a/input/reg_education.xlsx
+++ b/input/reg_education.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="98">
   <si>
     <t>Description:</t>
   </si>
@@ -318,7 +318,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="158">
+  <fonts count="325">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -958,6 +958,700 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -968,7 +1662,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="150">
+  <borders count="304">
     <border>
       <left/>
       <right/>
@@ -2019,11 +2713,1089 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -2618,6 +4390,622 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="182" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="183" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="184" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="185" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="186" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="187" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="188" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="189" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="190" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="191" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="192" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="193" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="194" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="195" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="196" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="197" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="198" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="199" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="200" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="201" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="202" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="203" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="204" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="205" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="206" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="207" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="208" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="209" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="210" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="211" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="212" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="213" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="214" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="215" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="216" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="217" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="218" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="219" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="220" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="221" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="222" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="223" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="224" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="225" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="226" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="227" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="228" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="229" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="230" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="231" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="232" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="233" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="234" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="235" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="236" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="237" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="238" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="239" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="240" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="241" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="242" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="243" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="244" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="245" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="246" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="247" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="248" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="249" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="250" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="251" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="252" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="253" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="254" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="255" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="256" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="257" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="258" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="259" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="260" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="261" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="262" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="263" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="264" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="265" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="266" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="267" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="268" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="269" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="270" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="271" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="272" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="273" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="274" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="275" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="276" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="277" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="278" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="279" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="280" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="281" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="282" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="283" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="284" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="285" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="286" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="287" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="288" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="289" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="290" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="291" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="292" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="293" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="294" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="295" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="296" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="297" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="298" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="299" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="300" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="301" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="302" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="303" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="304" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="305" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="306" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="307" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="308" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="309" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="310" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="311" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="312" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="313" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="314" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="315" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="316" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="317" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="318" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="319" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="320" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="321" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="322" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2634,7 +5022,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="155" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2658,10 +5046,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="157" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2698,7 +5086,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="158" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
@@ -2720,12 +5108,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="159" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="160" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2758,7 +5146,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="161" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2791,7 +5179,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="149" t="s">
+      <c r="A11" s="303" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8369,519 +10757,519 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="162" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="164" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="165" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="166" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="167">
         <v>-0.70269445766594751</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="168" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="169" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="170">
         <v>0.7021865775689643</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="171" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="172" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="173">
         <v>-0.0091555150716159557</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="174" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="175" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="176">
         <v>-0.36235547326872475</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="178" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="179">
         <v>-1.1278755901799129</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="180" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="182">
         <v>-0.34052897374964242</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="185">
         <v>-0.2058281598373842</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="188">
         <v>0.28530113479258173</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="190" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="191">
         <v>0.072134082402282695</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="192" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="193" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="194">
         <v>0.0016402789873566366</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="195" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="196" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="197">
         <v>0.093481552336863019</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="198" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="199" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="200">
         <v>0.12025768533834048</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="201" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="202" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="203">
         <v>-0.18487126222746433</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="204" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="206">
         <v>-0.21853624108533759</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="207" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="208" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="209">
         <v>0.64321632479633362</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="210" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="211" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="212">
         <v>-0.74273764434959522</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="213" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="61">
+      <c r="C18" s="215">
         <v>-0.043988276084517601</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="216" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="217" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="64">
+      <c r="C19" s="218">
         <v>-0.045405195870811474</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="s">
+      <c r="A20" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="67">
+      <c r="C20" s="221">
         <v>-0.0074294877842719384</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="223" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="70">
+      <c r="C21" s="224">
         <v>0.45087035665425657</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="225" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="226" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="73">
+      <c r="C22" s="227">
         <v>-0.861596101506236</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="228" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="229" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="230">
         <v>-0.16428306254050323</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="231" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="79">
+      <c r="C24" s="233">
         <v>-5.284505865695162</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="234" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="235" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="82">
+      <c r="C25" s="236">
         <v>0.087228707549441842</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="83" t="s">
+      <c r="A26" s="237" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="238" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="85">
+      <c r="C26" s="239">
         <v>1.1147671940833528</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="86" t="s">
+      <c r="A27" s="240" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="241" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="88">
+      <c r="C27" s="242">
         <v>-0.014490874588703895</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="243" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="90" t="s">
+      <c r="B28" s="244" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="91">
+      <c r="C28" s="245">
         <v>-0.36235547326872475</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="92" t="s">
+      <c r="A29" s="246" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="93" t="s">
+      <c r="B29" s="247" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="94">
+      <c r="C29" s="248">
         <v>-1.1278755901799129</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="95" t="s">
+      <c r="A30" s="249" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="250" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="97">
+      <c r="C30" s="251">
         <v>-0.34052897374964242</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="98" t="s">
+      <c r="A31" s="252" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="99" t="s">
+      <c r="B31" s="253" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="100">
+      <c r="C31" s="254">
         <v>-0.2058281598373842</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="256" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="103">
+      <c r="C32" s="257">
         <v>-0.46286116847873859</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="104" t="s">
+      <c r="A33" s="258" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="105" t="s">
+      <c r="B33" s="259" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="106">
+      <c r="C33" s="260">
         <v>0.072134082402282695</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="107" t="s">
+      <c r="A34" s="261" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="108" t="s">
+      <c r="B34" s="262" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="109">
+      <c r="C34" s="263">
         <v>0.0016402789873566366</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="110" t="s">
+      <c r="A35" s="264" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="111" t="s">
+      <c r="B35" s="265" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="112">
+      <c r="C35" s="266">
         <v>0.093481552336863019</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="267" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="268" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="115">
+      <c r="C36" s="269">
         <v>0.12025768533834048</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="116" t="s">
+      <c r="A37" s="270" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="117" t="s">
+      <c r="B37" s="271" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="118">
+      <c r="C37" s="272">
         <v>-0.18487126222746433</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="119" t="s">
+      <c r="A38" s="273" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="120" t="s">
+      <c r="B38" s="274" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="121">
+      <c r="C38" s="275">
         <v>-0.21853624108533759</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="122" t="s">
+      <c r="A39" s="276" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="123" t="s">
+      <c r="B39" s="277" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="124">
+      <c r="C39" s="278">
         <v>-0.69714558168500984</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="125" t="s">
+      <c r="A40" s="279" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="126" t="s">
+      <c r="B40" s="280" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="127">
+      <c r="C40" s="281">
         <v>-0.08350987592658568</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="128" t="s">
+      <c r="A41" s="282" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="129" t="s">
+      <c r="B41" s="283" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="130">
+      <c r="C41" s="284">
         <v>0.024101308431316013</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="131" t="s">
+      <c r="A42" s="285" t="s">
         <v>62</v>
       </c>
-      <c r="B42" s="132" t="s">
+      <c r="B42" s="286" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="133">
+      <c r="C42" s="287">
         <v>-0.045405195870811474</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="134" t="s">
+      <c r="A43" s="288" t="s">
         <v>62</v>
       </c>
-      <c r="B43" s="135" t="s">
+      <c r="B43" s="289" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="136">
+      <c r="C43" s="290">
         <v>-0.0074294877842719384</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="137" t="s">
+      <c r="A44" s="291" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="138" t="s">
+      <c r="B44" s="292" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="139">
+      <c r="C44" s="293">
         <v>0.45087035665425657</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="140" t="s">
+      <c r="A45" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="B45" s="141" t="s">
+      <c r="B45" s="295" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="142">
+      <c r="C45" s="296">
         <v>-0.861596101506236</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="143" t="s">
+      <c r="A46" s="297" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="144" t="s">
+      <c r="B46" s="298" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="145">
+      <c r="C46" s="299">
         <v>-0.16428306254050323</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="146" t="s">
+      <c r="A47" s="300" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="147" t="s">
+      <c r="B47" s="301" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="148">
+      <c r="C47" s="302">
         <v>-17.698016356937142</v>
       </c>
     </row>
